--- a/summary_graphics/demo_Psychotria_M0_1a_AIC.xlsx
+++ b/summary_graphics/demo_Psychotria_M0_1a_AIC.xlsx
@@ -1,22 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10311"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nmat471/Documents/GitHub/bgwk5/summary_graphics/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/System/Volumes/Data/GitHub/bgwk5/summary_graphics/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F59FC54D-8608-7A4A-A474-CBBC02CD2A5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A88CBAEC-E844-0544-85A3-20E668EF05E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="43860" windowHeight="24600" xr2:uid="{630A2355-7C92-714B-8701-15F8D109B3E6}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28000" windowHeight="17500" activeTab="2" xr2:uid="{630A2355-7C92-714B-8701-15F8D109B3E6}"/>
   </bookViews>
   <sheets>
     <sheet name="blank" sheetId="2" r:id="rId1"/>
     <sheet name="formulas" sheetId="3" r:id="rId2"/>
     <sheet name="filled_in" sheetId="1" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">filled_in!$A$2:$M$17</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -38,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="62">
   <si>
     <t>Example AIC table from scratch</t>
   </si>
@@ -203,6 +206,27 @@
   </si>
   <si>
     <t>=SUM(J5:J10)</t>
+  </si>
+  <si>
+    <t>%</t>
+  </si>
+  <si>
+    <t>AICc</t>
+  </si>
+  <si>
+    <t>BIC</t>
+  </si>
+  <si>
+    <t>BIC weight</t>
+  </si>
+  <si>
+    <t>DEC+J+w</t>
+  </si>
+  <si>
+    <t>DEC+w</t>
+  </si>
+  <si>
+    <t>w</t>
   </si>
 </sst>
 </file>
@@ -306,7 +330,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -339,6 +363,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -945,6 +970,7 @@
     <mergeCell ref="D3:G3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
@@ -1210,29 +1236,27 @@
     <mergeCell ref="D3:G3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A0959B2-D09E-1046-B7EB-3063FEC026C6}">
-  <dimension ref="A2:L12"/>
+  <dimension ref="A2:Q20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.6640625" customWidth="1"/>
     <col min="3" max="3" width="6.1640625" customWidth="1"/>
     <col min="4" max="7" width="8.83203125" customWidth="1"/>
-    <col min="8" max="8" width="7.6640625" customWidth="1"/>
-    <col min="10" max="10" width="7.83203125" customWidth="1"/>
-    <col min="11" max="11" width="7" customWidth="1"/>
-    <col min="12" max="12" width="7.83203125" customWidth="1"/>
+    <col min="8" max="12" width="6.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:17" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A3" s="8"/>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -1248,7 +1272,7 @@
       <c r="K3" s="8"/>
       <c r="L3" s="8"/>
     </row>
-    <row r="4" spans="1:12" s="1" customFormat="1" ht="68" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" s="1" customFormat="1" ht="55" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>1</v>
       </c>
@@ -1268,7 +1292,7 @@
         <v>11</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="H4" s="9" t="s">
         <v>13</v>
@@ -1285,8 +1309,20 @@
       <c r="L4" s="9" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="N4" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -1313,23 +1349,26 @@
         <v>73.08</v>
       </c>
       <c r="I5">
-        <f>H5-H$12</f>
-        <v>25.184882000000002</v>
+        <f>H5-H$20</f>
+        <v>33.73218</v>
       </c>
       <c r="J5">
         <f>EXP(-0.5*I5)</f>
-        <v>3.3976008764020256E-6</v>
+        <v>4.7331490588498745E-8</v>
       </c>
       <c r="K5">
-        <f>J5/J$12</f>
-        <v>1.4058516196965509E-6</v>
+        <f>J5/J$20</f>
+        <v>1.5662463155596895E-8</v>
       </c>
       <c r="L5" s="2">
         <f>K5*100</f>
-        <v>1.4058516196965509E-4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+        <v>1.5662463155596896E-6</v>
+      </c>
+      <c r="M5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1352,27 +1391,30 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <f t="shared" ref="H6:H10" si="0">-2*(B6-C6)</f>
+        <f t="shared" ref="H6:H18" si="0">-2*(B6-C6)</f>
         <v>47.895117999999997</v>
       </c>
       <c r="I6">
-        <f t="shared" ref="I6:I10" si="1">H6-H$12</f>
-        <v>0</v>
+        <f>H6-H$20</f>
+        <v>8.5472979999999978</v>
       </c>
       <c r="J6">
-        <f t="shared" ref="J6:J10" si="2">EXP(-0.5*I6)</f>
-        <v>1</v>
+        <f>EXP(-0.5*I6)</f>
+        <v>1.3930856598618969E-2</v>
       </c>
       <c r="K6">
-        <f t="shared" ref="K6:K10" si="3">J6/J$12</f>
-        <v>0.41377774224773356</v>
+        <f>J6/J$20</f>
+        <v>4.6098596407777755E-3</v>
       </c>
       <c r="L6" s="2">
-        <f t="shared" ref="L6:L10" si="4">K6*100</f>
-        <v>41.377774224773354</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+        <f t="shared" ref="L6:L18" si="1">K6*100</f>
+        <v>0.46098596407777753</v>
+      </c>
+      <c r="M6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -1399,23 +1441,26 @@
         <v>70.303399999999996</v>
       </c>
       <c r="I7">
+        <f>H7-H$20</f>
+        <v>30.955579999999998</v>
+      </c>
+      <c r="J7">
+        <f t="shared" ref="J6:J18" si="2">EXP(-0.5*I7)</f>
+        <v>1.897060629099175E-7</v>
+      </c>
+      <c r="K7">
+        <f>J7/J$20</f>
+        <v>6.2775631694175466E-8</v>
+      </c>
+      <c r="L7" s="2">
         <f t="shared" si="1"/>
-        <v>22.408282</v>
-      </c>
-      <c r="J7">
-        <f t="shared" si="2"/>
-        <v>1.3617688299851134E-5</v>
-      </c>
-      <c r="K7">
-        <f t="shared" si="3"/>
-        <v>5.6346963193457795E-6</v>
-      </c>
-      <c r="L7" s="2">
-        <f t="shared" si="4"/>
-        <v>5.6346963193457794E-4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+        <v>6.277563169417547E-6</v>
+      </c>
+      <c r="M7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -1442,23 +1487,26 @@
         <v>48.171999999999997</v>
       </c>
       <c r="I8">
-        <f t="shared" si="1"/>
-        <v>0.27688200000000052</v>
+        <f>H8-H$20</f>
+        <v>8.8241799999999984</v>
       </c>
       <c r="J8">
         <f t="shared" si="2"/>
-        <v>0.87071462191636018</v>
+        <v>1.2129800536237545E-2</v>
       </c>
       <c r="K8">
-        <f t="shared" si="3"/>
-        <v>0.36028233039864044</v>
+        <f>J8/J$20</f>
+        <v>4.0138721942073081E-3</v>
       </c>
       <c r="L8" s="2">
-        <f t="shared" si="4"/>
-        <v>36.028233039864041</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+        <f t="shared" si="1"/>
+        <v>0.4013872194207308</v>
+      </c>
+      <c r="M8" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -1485,23 +1533,26 @@
         <v>84.669219999999996</v>
       </c>
       <c r="I9">
-        <f t="shared" si="1"/>
-        <v>36.774101999999999</v>
+        <f>H9-H$20</f>
+        <v>45.321399999999997</v>
       </c>
       <c r="J9">
         <f t="shared" si="2"/>
-        <v>1.0342016164273005E-8</v>
+        <v>1.4407314412508662E-10</v>
       </c>
       <c r="K9">
-        <f t="shared" si="3"/>
-        <v>4.2792960987424496E-9</v>
+        <f>J9/J$20</f>
+        <v>4.7675242919953497E-11</v>
       </c>
       <c r="L9" s="2">
-        <f t="shared" si="4"/>
-        <v>4.2792960987424494E-7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>4.7675242919953499E-9</v>
+      </c>
+      <c r="M9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -1528,50 +1579,321 @@
         <v>49.1053</v>
       </c>
       <c r="I10">
-        <f t="shared" si="1"/>
-        <v>1.2101820000000032</v>
+        <f>H10-H$20</f>
+        <v>9.757480000000001</v>
       </c>
       <c r="J10">
         <f t="shared" si="2"/>
-        <v>0.54602473612783686</v>
+        <v>7.6065922982956578E-3</v>
       </c>
       <c r="K10">
-        <f t="shared" si="3"/>
-        <v>0.22593288252639079</v>
+        <f>J10/J$20</f>
+        <v>2.5170973939420498E-3</v>
       </c>
       <c r="L10" s="2">
-        <f t="shared" si="4"/>
-        <v>22.593288252639081</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="17" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
+        <f t="shared" si="1"/>
+        <v>0.25170973939420499</v>
+      </c>
+      <c r="M10" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>2</v>
+      </c>
+      <c r="B11" s="8">
+        <v>-31.411989999999999</v>
+      </c>
+      <c r="C11" s="8">
+        <v>2</v>
+      </c>
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
       <c r="F11" s="8"/>
       <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="8"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="F12" t="s">
+      <c r="H11">
+        <f>-2*(B11-C11)</f>
+        <v>66.823980000000006</v>
+      </c>
+      <c r="I11" s="8">
+        <f>H11-H$20</f>
+        <v>27.476160000000007</v>
+      </c>
+      <c r="J11" s="8">
+        <f t="shared" si="2"/>
+        <v>1.0805071972338944E-6</v>
+      </c>
+      <c r="K11" s="8">
+        <f>J11/J$20</f>
+        <v>3.5755062761842153E-7</v>
+      </c>
+      <c r="L11" s="8">
+        <f t="shared" si="1"/>
+        <v>3.575506276184215E-5</v>
+      </c>
+      <c r="M11" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12">
+        <v>-16.673909999999999</v>
+      </c>
+      <c r="C12" s="14">
+        <v>3</v>
+      </c>
+      <c r="H12">
+        <f t="shared" si="0"/>
+        <v>39.347819999999999</v>
+      </c>
+      <c r="I12" s="14">
+        <f>H12-H$20</f>
+        <v>0</v>
+      </c>
+      <c r="J12" s="14">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="K12" s="14">
+        <f>J12/J$20</f>
+        <v>0.33090999165369145</v>
+      </c>
+      <c r="L12" s="2">
+        <f t="shared" si="1"/>
+        <v>33.090999165369148</v>
+      </c>
+      <c r="M12" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13">
+        <v>-29.063210000000002</v>
+      </c>
+      <c r="C13" s="14">
+        <v>2</v>
+      </c>
+      <c r="H13">
+        <f t="shared" si="0"/>
+        <v>62.126420000000003</v>
+      </c>
+      <c r="I13" s="14">
+        <f>H13-H$20</f>
+        <v>22.778600000000004</v>
+      </c>
+      <c r="J13" s="14">
+        <f t="shared" si="2"/>
+        <v>1.1315919707889203E-5</v>
+      </c>
+      <c r="K13" s="14">
+        <f>J13/J$20</f>
+        <v>3.7445508960914587E-6</v>
+      </c>
+      <c r="L13" s="2">
+        <f t="shared" si="1"/>
+        <v>3.7445508960914589E-4</v>
+      </c>
+      <c r="M13" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>5</v>
+      </c>
+      <c r="B14">
+        <v>-16.880500000000001</v>
+      </c>
+      <c r="C14" s="14">
+        <v>3</v>
+      </c>
+      <c r="H14">
+        <f t="shared" si="0"/>
+        <v>39.761000000000003</v>
+      </c>
+      <c r="I14" s="14">
+        <f>H14-H$20</f>
+        <v>0.4131800000000041</v>
+      </c>
+      <c r="J14" s="14">
+        <f t="shared" si="2"/>
+        <v>0.81335305638770583</v>
+      </c>
+      <c r="K14" s="14">
+        <f>J14/J$20</f>
+        <v>0.26914665310076019</v>
+      </c>
+      <c r="L14" s="2">
+        <f t="shared" si="1"/>
+        <v>26.914665310076018</v>
+      </c>
+      <c r="M14" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15">
+        <v>-40.23236</v>
+      </c>
+      <c r="C15" s="14">
+        <v>2</v>
+      </c>
+      <c r="H15">
+        <f t="shared" si="0"/>
+        <v>84.46472</v>
+      </c>
+      <c r="I15" s="14">
+        <f>H15-H$20</f>
+        <v>45.116900000000001</v>
+      </c>
+      <c r="J15" s="14">
+        <f t="shared" si="2"/>
+        <v>1.5958410956480034E-10</v>
+      </c>
+      <c r="K15" s="14">
+        <f>J15/J$20</f>
+        <v>5.2807976364149861E-11</v>
+      </c>
+      <c r="L15" s="2">
+        <f t="shared" si="1"/>
+        <v>5.2807976364149864E-9</v>
+      </c>
+      <c r="M15" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16">
+        <v>-16.880510000000001</v>
+      </c>
+      <c r="C16" s="14">
+        <v>3</v>
+      </c>
+      <c r="H16">
+        <f t="shared" si="0"/>
+        <v>39.761020000000002</v>
+      </c>
+      <c r="I16" s="14">
+        <f>H16-H$20</f>
+        <v>0.41320000000000334</v>
+      </c>
+      <c r="J16" s="14">
+        <f t="shared" si="2"/>
+        <v>0.8133449228978098</v>
+      </c>
+      <c r="K16" s="14">
+        <f>J16/J$20</f>
+        <v>0.26914396164768656</v>
+      </c>
+      <c r="L16" s="2">
+        <f t="shared" si="1"/>
+        <v>26.914396164768657</v>
+      </c>
+      <c r="M16" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>60</v>
+      </c>
+      <c r="B17">
+        <v>-31.46575</v>
+      </c>
+      <c r="C17" s="14">
+        <v>3</v>
+      </c>
+      <c r="G17">
+        <v>2.4</v>
+      </c>
+      <c r="H17">
+        <f t="shared" si="0"/>
+        <v>68.9315</v>
+      </c>
+      <c r="I17" s="14">
+        <f>H17-H$20</f>
+        <v>29.583680000000001</v>
+      </c>
+      <c r="J17" s="14">
+        <f t="shared" si="2"/>
+        <v>3.7669123137303536E-7</v>
+      </c>
+      <c r="K17" s="14">
+        <f>J17/J$20</f>
+        <v>1.2465089222966989E-7</v>
+      </c>
+      <c r="L17" s="2">
+        <f t="shared" si="1"/>
+        <v>1.2465089222966988E-5</v>
+      </c>
+      <c r="M17" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>59</v>
+      </c>
+      <c r="B18">
+        <v>-16.69115</v>
+      </c>
+      <c r="C18" s="14">
+        <v>4</v>
+      </c>
+      <c r="G18">
+        <v>2.8</v>
+      </c>
+      <c r="H18">
+        <f t="shared" si="0"/>
+        <v>41.382300000000001</v>
+      </c>
+      <c r="I18" s="14">
+        <f>H18-H$20</f>
+        <v>2.0344800000000021</v>
+      </c>
+      <c r="J18" s="14">
+        <f t="shared" si="2"/>
+        <v>0.36159155690639538</v>
+      </c>
+      <c r="K18" s="14">
+        <f>J18/J$20</f>
+        <v>0.1196542590779406</v>
+      </c>
+      <c r="L18" s="2">
+        <f>K18*100</f>
+        <v>11.96542590779406</v>
+      </c>
+      <c r="M18" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="F20" t="s">
         <v>14</v>
       </c>
-      <c r="H12">
-        <f>MIN(H5:H10)</f>
-        <v>47.895117999999997</v>
-      </c>
-      <c r="I12" t="s">
+      <c r="H20">
+        <f>MIN(H5:H18)</f>
+        <v>39.347819999999999</v>
+      </c>
+      <c r="I20" t="s">
         <v>16</v>
       </c>
-      <c r="J12">
-        <f>SUM(J5:J10)</f>
-        <v>2.4167563836753896</v>
+      <c r="J20">
+        <f>SUM(J5:J18)</f>
+        <v>3.0219697960844107</v>
       </c>
     </row>
   </sheetData>
@@ -1579,6 +1901,7 @@
     <mergeCell ref="D3:H3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
